--- a/output/graficos_nacionales/plot_nacional_m_miginterna_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_miginterna_a_2023.xlsx
@@ -16233,7 +16233,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Migración interna neta</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_m_miginterna_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_miginterna_a_2023.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="734">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:21</t>
+    <t xml:space="preserve">2026-07-30 15:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2185,16 +2185,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_nacional_m_miginterna_a_2023.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Migracion interna neta</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Comuna (vista nacional macrozonal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
@@ -13647,23 +13656,23 @@
         <v>723</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
     </row>
   </sheetData>
@@ -13685,21 +13694,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13708,7 +13717,7 @@
         <v>2023</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_m_miginterna_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_miginterna_a_2023.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Macrozona Austral</t>
   </si>
   <si>
-    <t xml:space="preserve">value</t>
+    <t xml:space="preserve">Valor (por 1.000)</t>
   </si>
   <si>
     <t xml:space="preserve">Magallanes</t>
@@ -469,18 +469,18 @@
     <t xml:space="preserve">Río Claro</t>
   </si>
   <si>
+    <t xml:space="preserve">5102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casablanca</t>
+  </si>
+  <si>
     <t xml:space="preserve">7302</t>
   </si>
   <si>
     <t xml:space="preserve">Hualañé</t>
   </si>
   <si>
-    <t xml:space="preserve">5102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casablanca</t>
-  </si>
-  <si>
     <t xml:space="preserve">6104</t>
   </si>
   <si>
@@ -493,18 +493,18 @@
     <t xml:space="preserve">Isla de Maipo</t>
   </si>
   <si>
+    <t xml:space="preserve">5803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olmué</t>
+  </si>
+  <si>
     <t xml:space="preserve">16302</t>
   </si>
   <si>
     <t xml:space="preserve">Coihueco</t>
   </si>
   <si>
-    <t xml:space="preserve">5803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olmué</t>
-  </si>
-  <si>
     <t xml:space="preserve">5303</t>
   </si>
   <si>
@@ -679,18 +679,18 @@
     <t xml:space="preserve">Santa María</t>
   </si>
   <si>
+    <t xml:space="preserve">5401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Ligua</t>
+  </si>
+  <si>
     <t xml:space="preserve">16201</t>
   </si>
   <si>
     <t xml:space="preserve">Quirihue</t>
   </si>
   <si>
-    <t xml:space="preserve">5401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Ligua</t>
-  </si>
-  <si>
     <t xml:space="preserve">5702</t>
   </si>
   <si>
@@ -799,18 +799,18 @@
     <t xml:space="preserve">Palmilla</t>
   </si>
   <si>
+    <t xml:space="preserve">6110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mostazal</t>
+  </si>
+  <si>
     <t xml:space="preserve">7304</t>
   </si>
   <si>
     <t xml:space="preserve">Molina</t>
   </si>
   <si>
-    <t xml:space="preserve">6110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mostazal</t>
-  </si>
-  <si>
     <t xml:space="preserve">6111</t>
   </si>
   <si>
@@ -841,18 +841,18 @@
     <t xml:space="preserve">San Antonio</t>
   </si>
   <si>
+    <t xml:space="preserve">6106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graneros</t>
+  </si>
+  <si>
     <t xml:space="preserve">7201</t>
   </si>
   <si>
     <t xml:space="preserve">Cauquenes</t>
   </si>
   <si>
-    <t xml:space="preserve">6106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graneros</t>
-  </si>
-  <si>
     <t xml:space="preserve">7202</t>
   </si>
   <si>
@@ -1813,18 +1813,18 @@
     <t xml:space="preserve">14104</t>
   </si>
   <si>
+    <t xml:space="preserve">9205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lonquimay</t>
+  </si>
+  <si>
     <t xml:space="preserve">10207</t>
   </si>
   <si>
     <t xml:space="preserve">Queilén</t>
   </si>
   <si>
-    <t xml:space="preserve">9205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lonquimay</t>
-  </si>
-  <si>
     <t xml:space="preserve">10208</t>
   </si>
   <si>
@@ -2017,24 +2017,24 @@
     <t xml:space="preserve">Traiguén</t>
   </si>
   <si>
+    <t xml:space="preserve">8202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arauco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Angeles</t>
+  </si>
+  <si>
     <t xml:space="preserve">14102</t>
   </si>
   <si>
     <t xml:space="preserve">Corral</t>
   </si>
   <si>
-    <t xml:space="preserve">8202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arauco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Angeles</t>
-  </si>
-  <si>
     <t xml:space="preserve">8111</t>
   </si>
   <si>
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:28</t>
+    <t xml:space="preserve">2026-09-08 10:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2590,9 +2590,9 @@
     <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="19.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="12.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="19.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="10.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="14.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="19.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4712,10 +4712,10 @@
         <v>2023</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>150</v>
@@ -4744,10 +4744,10 @@
         <v>2023</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>152</v>
@@ -4840,10 +4840,10 @@
         <v>2023</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>158</v>
@@ -4872,10 +4872,10 @@
         <v>2023</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>160</v>
@@ -5832,10 +5832,10 @@
         <v>2023</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>220</v>
@@ -5864,10 +5864,10 @@
         <v>2023</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>222</v>
@@ -6472,10 +6472,10 @@
         <v>2023</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>260</v>
@@ -6504,10 +6504,10 @@
         <v>2023</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>262</v>
@@ -6696,10 +6696,10 @@
         <v>2023</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>274</v>
@@ -6728,10 +6728,10 @@
         <v>2023</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>276</v>
@@ -11720,10 +11720,10 @@
         <v>2023</v>
       </c>
       <c r="B286" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>598</v>
@@ -11752,10 +11752,10 @@
         <v>2023</v>
       </c>
       <c r="B287" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>600</v>
@@ -12808,10 +12808,10 @@
         <v>2023</v>
       </c>
       <c r="B320" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="D320" s="2" t="s">
         <v>666</v>
@@ -12872,10 +12872,10 @@
         <v>2023</v>
       </c>
       <c r="B322" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="D322" s="2" t="s">
         <v>670</v>
@@ -13687,7 +13687,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="19.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
   </cols>
